--- a/tame_output/ON/bt/strategyON_20240613.xlsx
+++ b/tame_output/ON/bt/strategyON_20240613.xlsx
@@ -47390,10 +47390,10 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-5.041890591038403</v>
+        <v>-5.042160336595285</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.138644183645012</v>
+        <v>1.138536285422259</v>
       </c>
       <c r="F1993" t="n">
         <v>-0.3290943718481369</v>

--- a/tame_output/ON/bt/strategyON_20240613.xlsx
+++ b/tame_output/ON/bt/strategyON_20240613.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-50.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.3%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.8%</t>
+          <t>-661.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-262.4%</t>
+          <t>-260.7%</t>
         </is>
       </c>
     </row>
@@ -47390,10 +47390,10 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-5.042160336595285</v>
+        <v>-5.000102759695992</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.138536285422259</v>
+        <v>1.155359316181976</v>
       </c>
       <c r="F1993" t="n">
         <v>-0.3290943718481369</v>

--- a/tame_output/ON/bt/strategyON_20240613.xlsx
+++ b/tame_output/ON/bt/strategyON_20240613.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-150.2%</t>
+          <t>-123.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1993"/>
+  <dimension ref="A1:G1994"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102496</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.829580423509134</v>
+        <v>3.814259761756002</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
@@ -47400,6 +47400,29 @@
       </c>
       <c r="G1993" t="n">
         <v>2.958300221265239</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="2" t="n">
+        <v>45456</v>
+      </c>
+      <c r="B1994" t="n">
+        <v>3.829564997254509</v>
+      </c>
+      <c r="C1994" t="n">
+        <v>3.229112940793623</v>
+      </c>
+      <c r="D1994" t="n">
+        <v>-5.000102759695992</v>
+      </c>
+      <c r="E1994" t="n">
+        <v>1.155359316181976</v>
+      </c>
+      <c r="F1994" t="n">
+        <v>-0.3290943718481369</v>
+      </c>
+      <c r="G1994" t="n">
+        <v>3.222176737779991</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240613.xlsx
+++ b/tame_output/ON/bt/strategyON_20240613.xlsx
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.829564997254509</v>
+        <v>3.82956499725451</v>
       </c>
       <c r="C1994" t="n">
         <v>3.229112940793623</v>

--- a/tame_output/ON/bt/strategyON_20240613.xlsx
+++ b/tame_output/ON/bt/strategyON_20240613.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>453.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-661.6%</t>
+          <t>-660.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-260.7%</t>
+          <t>-260.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.0%</t>
+          <t>-162.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-256.9%</t>
+          <t>-256.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-123.8%</t>
+          <t>-149.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1994"/>
+  <dimension ref="A1:G1993"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.812124976550664</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.040377906118704</v>
+        <v>-5.031028727983996</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7972516865040231</v>
+        <v>0.8009913577579062</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4293557090164672</v>
+        <v>-0.420006530881759</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.556145847855372</v>
+        <v>2.561755354736197</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821832518758265</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.032423935823932</v>
+        <v>-5.023074757689224</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8004332746219318</v>
+        <v>0.8041729458758153</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4293557090164672</v>
+        <v>-0.420006530881759</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.556145847855372</v>
+        <v>2.561755354736197</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833281549842624</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.022050559490845</v>
+        <v>-5.012701381356137</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8109643821829713</v>
+        <v>0.8147040534368544</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.41898233268338</v>
+        <v>-0.4096331545486717</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.568751630683029</v>
+        <v>2.574361137563854</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822948612221917</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.894366249696549</v>
+        <v>-4.88501707156184</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8669304794754147</v>
+        <v>0.870670150729298</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2912980228890835</v>
+        <v>-0.2819488447543753</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.650254589934331</v>
+        <v>2.655864096815157</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.829079279209592</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.955032840098937</v>
+        <v>-4.94568366196423</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8294185157903313</v>
+        <v>0.8331581870442144</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3729963396076172</v>
+        <v>-0.3636471614729089</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.587990272379083</v>
+        <v>2.593599779259908</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690026</v>
+        <v>3.817107435585068</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.890038980165292</v>
+        <v>-4.880689802030584</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8595137623744182</v>
+        <v>0.8632534336283011</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3461657250034618</v>
+        <v>-0.3368165468687536</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.608186343752205</v>
+        <v>2.61379585063303</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.818202756569351</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.99079761592229</v>
+        <v>-4.981448437787583</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8233712477026969</v>
+        <v>0.82711091895658</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4349912937304672</v>
+        <v>-0.425642115595759</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.55905194214708</v>
+        <v>2.564661449027905</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.82695514705826</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.946594778836389</v>
+        <v>-4.937245600701682</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8469319850648942</v>
+        <v>0.8506716563187773</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.3907884566445668</v>
+        <v>-0.3814392785098585</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.591453246926458</v>
+        <v>2.597062753807283</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838470030917945</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.983573806499832</v>
+        <v>-4.974224628365125</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8305503744687648</v>
+        <v>0.8342900457226476</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.3538145548532363</v>
+        <v>-0.344465376718528</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.612047588470503</v>
+        <v>2.617657095351329</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.864165481937179</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.003631885364673</v>
+        <v>-4.994282707229965</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8737749081058681</v>
+        <v>0.877514579359751</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.3538145548532363</v>
+        <v>-0.344465376718528</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.663295353653543</v>
+        <v>2.668904860534368</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.86560908297332</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.963701212186782</v>
+        <v>-4.954352034052075</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8881878819712774</v>
+        <v>0.8919275532251603</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.3138838816753459</v>
+        <v>-0.3045347035406377</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.68569446215453</v>
+        <v>2.691303969035356</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864760244127436</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.923230864624077</v>
+        <v>-4.91388168648937</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.8993242492346294</v>
+        <v>0.9030639204885123</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.273413534112641</v>
+        <v>-0.2640643559779327</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.704924898930424</v>
+        <v>2.710534405811248</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162109</v>
+        <v>3.842817762057151</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.858006683496872</v>
+        <v>-4.848657505362165</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9426013257782164</v>
+        <v>0.9463409970320993</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.2081893529854353</v>
+        <v>-0.1988401748507271</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.761246811699452</v>
+        <v>2.766856318580277</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639815</v>
+        <v>3.840331588534856</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.908500973853928</v>
+        <v>-4.899151795719221</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9183645819346744</v>
+        <v>0.9221042531885573</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.2532100901115096</v>
+        <v>-0.2438609119768013</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.730195341723087</v>
+        <v>2.735804848603912</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.845440210644959</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.928612629888637</v>
+        <v>-4.919263451753929</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9115767118520313</v>
+        <v>0.9153163831059143</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.2421827451140904</v>
+        <v>-0.2328335669793821</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.738068541052779</v>
+        <v>2.743678047933604</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393543</v>
+        <v>3.828931847288585</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.026293209161283</v>
+        <v>-5.016944031026576</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.033062251164183</v>
+        <v>1.036801922418066</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.3528859404542792</v>
+        <v>-0.3435367623195709</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.832204394869877</v>
+        <v>2.837813901750702</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714881</v>
+        <v>3.813493222609923</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.00250164055514</v>
+        <v>-4.993152462420433</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.162691787824458</v>
+        <v>1.166431459078341</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.3290943718481369</v>
+        <v>-0.3197451937134286</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.96659224525138</v>
+        <v>2.972201752132204</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,45 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756002</v>
+        <v>3.813906087681373</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-5.000102759695992</v>
+        <v>-4.990753581561285</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.155359316181976</v>
+        <v>1.159098987435859</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.3290943718481369</v>
+        <v>-0.3197451937134286</v>
       </c>
       <c r="G1993" t="n">
-        <v>2.958300221265239</v>
-      </c>
-    </row>
-    <row r="1994">
-      <c r="A1994" s="2" t="n">
-        <v>45456</v>
-      </c>
-      <c r="B1994" t="n">
-        <v>3.82956499725451</v>
-      </c>
-      <c r="C1994" t="n">
-        <v>3.229112940793623</v>
-      </c>
-      <c r="D1994" t="n">
-        <v>-5.000102759695992</v>
-      </c>
-      <c r="E1994" t="n">
-        <v>1.155359316181976</v>
-      </c>
-      <c r="F1994" t="n">
-        <v>-0.3290943718481369</v>
-      </c>
-      <c r="G1994" t="n">
-        <v>3.222176737779991</v>
+        <v>2.963909728146063</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240613.xlsx
+++ b/tame_output/ON/bt/strategyON_20240613.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>43.9%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-50.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.1%</t>
+          <t>451.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.6%</t>
+          <t>-668.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-36.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-260.3%</t>
+          <t>-253.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-162.0%</t>
+          <t>-161.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-256.0%</t>
+          <t>-256.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-149.6%</t>
+          <t>-140.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1993"/>
+  <dimension ref="A1:G1994"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612276</v>
+        <v>3.346417924612275</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.31188830135569</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.053768106021697</v>
       </c>
       <c r="D1904" t="n">
         <v>-8.483707566215795</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2379804369511609</v>
+        <v>-0.3400713447783685</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.924368676976425</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.00123780766305</v>
+        <v>1.899146899835843</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.049135592768724</v>
       </c>
       <c r="D1905" t="n">
         <v>-8.351432092584908</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1897027607517789</v>
+        <v>-0.2917936685789866</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.792093203345538</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.075970578588609</v>
+        <v>1.973879670761401</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.051950653456361</v>
       </c>
       <c r="D1906" t="n">
         <v>-8.160832417911754</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1106478301948806</v>
+        <v>-0.2127387380220882</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.601493528672385</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.193145444080137</v>
+        <v>2.09105453625293</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.064856994680019</v>
       </c>
       <c r="D1907" t="n">
         <v>-7.911832619228173</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.001858430502210684</v>
+        <v>-0.100232477324997</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.601493528672385</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.206051785303796</v>
+        <v>2.103960877476589</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>2.936881065080801</v>
       </c>
       <c r="D1908" t="n">
         <v>-8.017422609001278</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.16835349500625</v>
+        <v>-0.2704444028334576</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.70708351844549</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.014721861840715</v>
+        <v>1.912630954013507</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>2.985425406957887</v>
       </c>
       <c r="D1909" t="n">
         <v>-8.036157511119875</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1273031139766023</v>
+        <v>-0.22939402180381</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.712679528105621</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.059908597921723</v>
+        <v>1.957817690094515</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710807</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.86554648426972</v>
       </c>
       <c r="D1910" t="n">
         <v>-7.888217469712275</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1880060201017302</v>
+        <v>-0.2900969279289378</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.692358612197063</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.95222222477869</v>
+        <v>1.850131316951482</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.856832498016241</v>
       </c>
       <c r="D1911" t="n">
         <v>-7.871059319580981</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1898567463026906</v>
+        <v>-0.2919476541298982</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.675200462065769</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.953803128603988</v>
+        <v>1.85171222077678</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.849871885921148</v>
       </c>
       <c r="D1912" t="n">
         <v>-7.827510912810291</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1793979956895075</v>
+        <v>-0.2814889035167152</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.675200462065769</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.946842516508895</v>
+        <v>1.844751608681687</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.864334240302291</v>
       </c>
       <c r="D1913" t="n">
         <v>-7.585362519356432</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.06807628392682119</v>
+        <v>-0.1701671917540288</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.675200462065769</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.961304870890038</v>
+        <v>1.85921396306283</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.858866360761486</v>
       </c>
       <c r="D1914" t="n">
         <v>-7.477103382233911</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.03024050861861749</v>
+        <v>-0.1323314164458251</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.675200462065769</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.955836991349233</v>
+        <v>1.853746083522025</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.856364454772063</v>
       </c>
       <c r="D1915" t="n">
         <v>-7.35381224741678</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.01657403931881163</v>
+        <v>-0.08551686850839602</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.551909327248639</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.027309766250088</v>
+        <v>1.92521885842288</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.864065433009388</v>
       </c>
       <c r="D1916" t="n">
         <v>-7.332663048513337</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.03273469711751398</v>
+        <v>-0.06935621070969367</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.530760128345195</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.047700263829479</v>
+        <v>1.945609356002271</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.859846141356439</v>
       </c>
       <c r="D1917" t="n">
         <v>-7.088897606529892</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1260215822579425</v>
+        <v>0.02393067443073482</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.530760128345195</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.04348097217653</v>
+        <v>1.941390064349322</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.861970455276455</v>
       </c>
       <c r="D1918" t="n">
         <v>-6.987134786252597</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1688510242888763</v>
+        <v>0.06676011646166868</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.517541059952767</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.053536727132003</v>
+        <v>1.951445819304795</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279181</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.854712530260157</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.737284392303523</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2615332568522084</v>
+        <v>0.1594423490250008</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.517541059952767</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.046278802115705</v>
+        <v>1.944187894288498</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.858311653780806</v>
       </c>
       <c r="D1920" t="n">
         <v>-6.56139229983609</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3354892173598305</v>
+        <v>0.2333983095326229</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.517541059952767</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.049877925636354</v>
+        <v>1.947787017809146</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.87163915983536</v>
       </c>
       <c r="D1921" t="n">
         <v>-6.389945836813626</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4173953086233695</v>
+        <v>0.3153044007961618</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.346094596930303</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.166073309504386</v>
+        <v>2.063982401677178</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.870659637451657</v>
       </c>
       <c r="D1922" t="n">
         <v>-6.164912837144803</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5064289861071956</v>
+        <v>0.4043380782799879</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.12106159726148</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.300113586921976</v>
+        <v>2.198022679094769</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.875354438505974</v>
       </c>
       <c r="D1923" t="n">
         <v>-6.101277094910869</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5365780840550864</v>
+        <v>0.4344871762278788</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.057425855027546</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.342989833316654</v>
+        <v>2.240898925489446</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074778</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.85654869728977</v>
       </c>
       <c r="D1924" t="n">
         <v>-6.057514913605027</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5352772153612189</v>
+        <v>0.4331863075340112</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.057425855027546</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.32418409210045</v>
+        <v>2.222093184273242</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.858291773914647</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.817084416800167</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6331924907080406</v>
+        <v>0.531101582880833</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8169953582226857</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.470185466808243</v>
+        <v>2.368094558981036</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.862221087749467</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.744841848628973</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6660188318113387</v>
+        <v>0.5639279239841311</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8169953582226857</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.474114780643064</v>
+        <v>2.372023872815856</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.862899671666807</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.691843526347585</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6878967446412338</v>
+        <v>0.5858058368140262</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7616590992207468</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.507995119961567</v>
+        <v>2.405904212134359</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.859897742886801</v>
       </c>
       <c r="D1928" t="n">
         <v>-5.583038640867858</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7284167700531179</v>
+        <v>0.6263258622259102</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7616590992207468</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.504993191181561</v>
+        <v>2.402902283354353</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.861476779897415</v>
       </c>
       <c r="D1929" t="n">
         <v>-5.363017842830847</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8180041262785362</v>
+        <v>0.7159132184513286</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.6204392541527666</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.591304135232963</v>
+        <v>2.489213227405755</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.877370962699238</v>
       </c>
       <c r="D1930" t="n">
         <v>-5.230150153767569</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8870453847056705</v>
+        <v>0.7849544768784629</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6204392541527666</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.607198318034786</v>
+        <v>2.505107410207578</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.87851680713954</v>
       </c>
       <c r="D1931" t="n">
         <v>-5.109977070403071</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9362604624917719</v>
+        <v>0.8341695546645642</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5002661707882676</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.680448012493788</v>
+        <v>2.57835710466658</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.88860490970098</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.965304925303333</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.004217423093107</v>
+        <v>0.9021265152658993</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3555940256885302</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.77733940211507</v>
+        <v>2.675248494287862</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.874642401102406</v>
       </c>
       <c r="D1933" t="n">
         <v>-5.025179752661026</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9663049835514559</v>
+        <v>0.8642140757242482</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4154688530462223</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.72745199710188</v>
+        <v>2.625361089274672</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>2.897042894424972</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.938380254882016</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.023425275985625</v>
+        <v>0.9213343681584178</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4154688530462223</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.749852490424446</v>
+        <v>2.647761582597238</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>2.897115295798384</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.940849961343822</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.022509794774315</v>
+        <v>0.9204188869471077</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4179385595080285</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.748443067920775</v>
+        <v>2.646352160093567</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>2.908122218273086</v>
       </c>
       <c r="D1936" t="n">
         <v>-5.009220147667833</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.006168642719413</v>
+        <v>0.9040777348922058</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4086628604718135</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.765015409817206</v>
+        <v>2.662924501989998</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>2.898558926904977</v>
       </c>
       <c r="D1937" t="n">
         <v>-5.117758328583967</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9531900789848509</v>
+        <v>0.8510991711576432</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4086628604718135</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.755452118449097</v>
+        <v>2.653361210621889</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.723268491945364</v>
       </c>
       <c r="D1938" t="n">
         <v>-5.148751487912672</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7655023802937557</v>
+        <v>0.6634114724665481</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4086628604718135</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.580161683489484</v>
+        <v>2.478070775662276</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.727835723937152</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.973277228120203</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8402593162025309</v>
+        <v>0.7381684083753233</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4086628604718135</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.584728915481271</v>
+        <v>2.482638007654064</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.703577752698359</v>
       </c>
       <c r="D1940" t="n">
         <v>-5.084213480761452</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7716268439072382</v>
+        <v>0.6695359360800306</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4086628604718135</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.560470944242478</v>
+        <v>2.458380036415271</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.706709137918264</v>
       </c>
       <c r="D1941" t="n">
         <v>-5.092495554906511</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7714453994691204</v>
+        <v>0.6693544916419127</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.4169449346168719</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.558633084975349</v>
+        <v>2.456542177148142</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.716881524350397</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.934569955971218</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8447880254753701</v>
+        <v>0.7426971176481625</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.4169449346168719</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.568805471407482</v>
+        <v>2.466714563580274</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742296</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.711827794924257</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.84832649294484</v>
+        <v>-4.894729045099032</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8742316812597815</v>
+        <v>0.7535797525708969</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.4169449346168719</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.563751741981342</v>
+        <v>2.461660834154134</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.703603570368783</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.89363331234382</v>
+        <v>-4.940035864498012</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8478847289447151</v>
+        <v>0.7272328002558306</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4577550976261027</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.531041419620329</v>
+        <v>2.428950511793121</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803188</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.704155443401884</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.922666417046121</v>
+        <v>-4.969068969200313</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8368233600968962</v>
+        <v>0.7161714314080116</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4577550976261027</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.53159329265343</v>
+        <v>2.429502384826223</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.63342813529325</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.829855935595261</v>
+        <v>-4.876258487749453</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8032202445686059</v>
+        <v>0.6825683158797213</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3649446161752434</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.516552273415312</v>
+        <v>2.414461365588104</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.635301611217851</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.874245404924689</v>
+        <v>-4.920647957078881</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7873379327614356</v>
+        <v>0.6666860040725511</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.409334085504671</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.491792067742256</v>
+        <v>2.389701159915048</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472735</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.630377319729574</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.761574186688438</v>
+        <v>-4.807976738842631</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8274821285676586</v>
+        <v>0.706830199878774</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2966628672684208</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.554470507195729</v>
+        <v>2.452379599368522</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.635868615560241</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.649197185505765</v>
+        <v>-4.695599737659958</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.877924224871395</v>
+        <v>0.7572722961825105</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2966628672684208</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.559961803026396</v>
+        <v>2.457870895199189</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.64736581732878</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.847431754392496</v>
+        <v>-4.893834306546688</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8101275990852419</v>
+        <v>0.6894756703963574</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.4948974361551514</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.452518263462897</v>
+        <v>2.35042735563569</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.485721537329433</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.930433035417775</v>
+        <v>-4.976835587571967</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6152828066757836</v>
+        <v>0.4946308779868991</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5134683206823252</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.279731452747246</v>
+        <v>2.177640544920038</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.605871198048639</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.039047113861106</v>
+        <v>-5.085449666015299</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6919868360176569</v>
+        <v>0.5713349073287723</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5134683206823252</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.399881113466451</v>
+        <v>2.297790205639244</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.620384224150962</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.125645696842209</v>
+        <v>-5.172048248996401</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6718604289275385</v>
+        <v>0.551208500238654</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5134683206823252</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.414394139568774</v>
+        <v>2.312303231741567</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.617803665493331</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.087262034284058</v>
+        <v>-5.13366458643825</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6846333352931677</v>
+        <v>0.5639814066042832</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.475084658124174</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.434843778446034</v>
+        <v>2.332752870618827</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.614532694338632</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.910145704248892</v>
+        <v>-4.956548256403084</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7522088961525359</v>
+        <v>0.6315569674636514</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.475084658124174</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.431572807291336</v>
+        <v>2.329481899464128</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.615216086100546</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.955237949082438</v>
+        <v>-5.00164050123663</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7348553899810308</v>
+        <v>0.6142034612921463</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5369807012935638</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.395118573151615</v>
+        <v>2.293027665324407</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.60900306140696</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.77586252784367</v>
+        <v>-4.822265079997862</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8003925337829523</v>
+        <v>0.6797406050940678</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.3802039431228451</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.482971603360461</v>
+        <v>2.380880695533253</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.58981051673855</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.820876741364277</v>
+        <v>-4.867279293518468</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7631943037062994</v>
+        <v>0.6425423750174151</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.4105528384374497</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.445569721503288</v>
+        <v>2.34347881367608</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.595502079077495</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.087881251636712</v>
+        <v>-5.134283803790903</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6620840619362709</v>
+        <v>0.5414321332473868</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.6049158764803984</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.334643461016464</v>
+        <v>2.232552553189257</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760807</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.594706000973997</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.189079033073885</v>
+        <v>-5.235481585228076</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6208088712579034</v>
+        <v>0.5001569425690193</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.6733246900257175</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.292802094785774</v>
+        <v>2.190711186958567</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.667265825912802</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.156603446903112</v>
+        <v>-5.203005999057304</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6313990672805292</v>
+        <v>0.5857070019761332</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.6733246900257175</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.290402056340091</v>
+        <v>2.263271011897372</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.663790545121047</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.137565319195815</v>
+        <v>-5.183967871350006</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6355390375716929</v>
+        <v>0.5898469722672974</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.731508301356912</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.252016608749619</v>
+        <v>2.2248855643069</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.841372414059728</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.168691950346433</v>
+        <v>-5.215094502500625</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.800670254050126</v>
+        <v>0.7549781887457305</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.731508301356912</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.4295984776883</v>
+        <v>2.402467433245581</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.842205743045861</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.221012330947225</v>
+        <v>-5.267414883101416</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7805754307959427</v>
+        <v>0.7348833654915472</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.6965614413480399</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.451399922679756</v>
+        <v>2.424268878237037</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.848214273442787</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.241269629476183</v>
+        <v>-5.287672181630374</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7784810417812857</v>
+        <v>0.7327889764768902</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.6965614413480399</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.457408453076682</v>
+        <v>2.430277408633963</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>2.927366921234809</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.093526659241181</v>
+        <v>-5.139929211395372</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9167308776673084</v>
+        <v>0.8710388123629129</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.5287540841131567</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.637245515209634</v>
+        <v>2.610114470766915</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.93016054276629</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.195541341772402</v>
+        <v>-5.241943893926593</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8787186261863011</v>
+        <v>0.8330265608819056</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.5287540841131567</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.640039136741115</v>
+        <v>2.612908092298396</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.930822891157948</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.189388635719618</v>
+        <v>-5.235791187873809</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8818420569990733</v>
+        <v>0.8361499916946777</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.5226013780603724</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.644393108764444</v>
+        <v>2.617262064321725</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.929903367898059</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.206197933870119</v>
+        <v>-5.252600486024311</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8741988144789827</v>
+        <v>0.8285067491745872</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.5394106762108741</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.633388006614254</v>
+        <v>2.606256962171535</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>2.996238921694879</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.143899935093997</v>
+        <v>-5.190302487248188</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9654535677862524</v>
+        <v>0.9197615024818568</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.5394106762108741</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.699723560411075</v>
+        <v>2.672592515968355</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.704819794084278</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.942109737428839</v>
+        <v>-4.988512289583031</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7547505192417137</v>
+        <v>0.7090584539373181</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.3413924840417197</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.527115348101965</v>
+        <v>2.499984303659246</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.775110026406453</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.882219055786246</v>
+        <v>-4.928621607940437</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8489970242209262</v>
+        <v>0.8033049589165306</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.2815018023991263</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.633339989409696</v>
+        <v>2.606208944966977</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.789737762522496</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.97995960041122</v>
+        <v>-5.026362152565412</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8245285424869802</v>
+        <v>0.7788364771825846</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.2973910805321064</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.638434158645952</v>
+        <v>2.611303114203233</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.788273743347168</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.15629736053415</v>
+        <v>-5.202699912688341</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7525294192624798</v>
+        <v>0.7068373539580843</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.4737288406550358</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.531167483396866</v>
+        <v>2.504036438954147</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.786765361387097</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.084751037757273</v>
+        <v>-5.131153589911464</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7796395664131595</v>
+        <v>0.7339475011087639</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.4737288406550358</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.529659101436795</v>
+        <v>2.502528056994076</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.812124976550664</v>
+        <v>3.83602339102496</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.786628228822533</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.031028727983996</v>
+        <v>-5.086780458272895</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8009913577579062</v>
+        <v>0.7515596211996276</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.420006530881759</v>
+        <v>-0.4293557090164672</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.561755354736197</v>
+        <v>2.529014803412653</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821832518758265</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.786628228822533</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.023074757689224</v>
+        <v>-5.078826487978123</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8041729458758153</v>
+        <v>0.7547412093175363</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.420006530881759</v>
+        <v>-0.4293557090164672</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.561755354736197</v>
+        <v>2.529014803412653</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833281549842624</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.793009985850337</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.012701381356137</v>
+        <v>-5.068453111645036</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8147040534368544</v>
+        <v>0.7652723168785753</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4096331545486717</v>
+        <v>-0.41898233268338</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.574361137563854</v>
+        <v>2.541620586240309</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822948612221917</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.797902359225062</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.88501707156184</v>
+        <v>-4.94076880185074</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.870670150729298</v>
+        <v>0.8212384141710185</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2819488447543753</v>
+        <v>-0.2912980228890835</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.655864096815157</v>
+        <v>2.623123545491612</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.829079279209592</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.784657031700934</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.94568366196423</v>
+        <v>-5.001435392253128</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8331581870442144</v>
+        <v>0.7837264504859354</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3636471614729089</v>
+        <v>-0.3729963396076172</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.593599779259908</v>
+        <v>2.560859227936364</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.817107435585068</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.788754734311563</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.880689802030584</v>
+        <v>-4.936441532319483</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8632534336283011</v>
+        <v>0.8138216970700221</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3368165468687536</v>
+        <v>-0.3461657250034618</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.61379585063303</v>
+        <v>2.581055299309486</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.818202756569351</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.792915673942641</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.981448437787583</v>
+        <v>-5.037200168076481</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.82711091895658</v>
+        <v>0.7776791823983009</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.425642115595759</v>
+        <v>-0.4349912937304672</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.564661449027905</v>
+        <v>2.531920897704361</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82695514705826</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.798795276470478</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.937245600701682</v>
+        <v>-4.992997330990581</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8506716563187773</v>
+        <v>0.8012399197604982</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.3814392785098585</v>
+        <v>-0.3907884566445668</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.597062753807283</v>
+        <v>2.564322202483738</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838470030917945</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.797205276939725</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.974224628365125</v>
+        <v>-5.029976358654023</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8342900457226476</v>
+        <v>0.7848583091643686</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.344465376718528</v>
+        <v>-0.3538145548532363</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.617657095351329</v>
+        <v>2.584916544027784</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.864165481937179</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.848453042122765</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.994282707229965</v>
+        <v>-5.050034437518864</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.877514579359751</v>
+        <v>0.8280828428014719</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.344465376718528</v>
+        <v>-0.3538145548532363</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.668904860534368</v>
+        <v>2.636164309210824</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86560908297332</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.846893746717018</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.954352034052075</v>
+        <v>-5.010103764340974</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8919275532251603</v>
+        <v>0.8424958166668812</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.3045347035406377</v>
+        <v>-0.3138838816753459</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.691303969035356</v>
+        <v>2.658563417711811</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864760244127436</v>
+        <v>3.864518876232396</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.841841974955288</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.91388168648937</v>
+        <v>-4.969633416778269</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9030639204885123</v>
+        <v>0.8536321839302334</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.2640643559779327</v>
+        <v>-0.273413534112641</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.710534405811248</v>
+        <v>2.677793854487704</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842817762057151</v>
+        <v>3.842576394162111</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.859029379047993</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.848657505362165</v>
+        <v>-4.904409235651063</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9463409970320993</v>
+        <v>0.8969092604738205</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.1988401748507271</v>
+        <v>-0.2081893529854353</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.766856318580277</v>
+        <v>2.734115767256732</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840331588534856</v>
+        <v>3.840090220639817</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.854990351347273</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.899151795719221</v>
+        <v>-4.95490352600812</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9221042531885573</v>
+        <v>0.8726725166302782</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.2438609119768013</v>
+        <v>-0.2532100901115096</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.735804848603912</v>
+        <v>2.703064297280368</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845440210644959</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.856247143678514</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.919263451753929</v>
+        <v>-4.975015182042828</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9153163831059143</v>
+        <v>0.8658846465476353</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.2328335669793821</v>
+        <v>-0.2421827451140904</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.743678047933604</v>
+        <v>2.71093749661006</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828931847288585</v>
+        <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.016804914699724</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.016944031026576</v>
+        <v>-5.072695761315474</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.036801922418066</v>
+        <v>0.9873701858597874</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.3435367623195709</v>
+        <v>-0.3528859404542792</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.837813901750702</v>
+        <v>2.805073350427157</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813493222609923</v>
+        <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.136917823917542</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.993152462420433</v>
+        <v>-5.048904192709331</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.166431459078341</v>
+        <v>1.116999722520062</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.3197451937134286</v>
+        <v>-0.3290943718481369</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.972201752132204</v>
+        <v>2.93946120080866</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,45 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.813906087681373</v>
+        <v>3.71523504607733</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.128625799931401</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.990753581561285</v>
+        <v>-5.085658611271054</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.159098987435859</v>
+        <v>1.094005931109232</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.3197451937134286</v>
+        <v>-0.3290943718481369</v>
       </c>
       <c r="G1993" t="n">
-        <v>2.963909728146063</v>
+        <v>2.931169176822519</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="2" t="n">
+        <v>45456</v>
+      </c>
+      <c r="B1994" t="n">
+        <v>3.720049849500817</v>
+      </c>
+      <c r="C1994" t="n">
+        <v>3.25677692125008</v>
+      </c>
+      <c r="D1994" t="n">
+        <v>-5.070772598716863</v>
+      </c>
+      <c r="E1994" t="n">
+        <v>1.228111457449587</v>
+      </c>
+      <c r="F1994" t="n">
+        <v>-0.3290943718481369</v>
+      </c>
+      <c r="G1994" t="n">
+        <v>3.059320298141198</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240613.xlsx
+++ b/tame_output/ON/bt/strategyON_20240613.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>50.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>-5.7%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.9%</t>
+          <t>452.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-668.6%</t>
+          <t>-676.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-41.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-36.6%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>-168.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-253.4%</t>
+          <t>-276.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-256.9%</t>
+          <t>-274.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-140.1%</t>
+          <t>-170.2%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.502790399141698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16374490944933</v>
+        <v>-10.03435202739345</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.925534295838232</v>
+        <v>-0.8737771430158787</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.312265601438336</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.752960731392246</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.30555468365612</v>
+        <v>-10.17616180160023</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9777756510365117</v>
+        <v>-0.9260184982141575</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.469437978585626</v>
+        <v>-2.483544399083911</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.663139859588308</v>
+        <v>1.654676007289337</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.23208485198867</v>
+        <v>-10.10269196993278</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9330160168761106</v>
+        <v>-0.8812588640537573</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.395968146918177</v>
+        <v>-2.410074567416463</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.722593460082198</v>
+        <v>1.714129607783227</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.40720926937521</v>
+        <v>-10.27781638731933</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9885105630832109</v>
+        <v>-0.9367534102608577</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.585198984803007</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632074030397789</v>
+        <v>1.623610178098817</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.6416613633897</v>
+        <v>-10.51226848133382</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.089510565590603</v>
+        <v>-1.03775341276825</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.585198984803007</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.624854865496193</v>
+        <v>1.616391013197221</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.92946520792694</v>
+        <v>-10.80007232587106</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.211304294179474</v>
+        <v>-1.159547141357121</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.858896408841959</v>
+        <v>-2.873002829340245</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.445500367999874</v>
+        <v>1.437036515700902</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.98225136352727</v>
+        <v>-10.85285848147138</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.231302966581049</v>
+        <v>-1.179545813758695</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.954571895424356</v>
+        <v>-2.968678315922642</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.389210865888992</v>
+        <v>1.38074701359002</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.10828815689556</v>
+        <v>-10.97889527483967</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.27902395529925</v>
+        <v>-1.227266802476896</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.9434266931129</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.407055568203952</v>
+        <v>1.39859171590498</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.05627264292674</v>
+        <v>-10.92687976087086</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.254227414025324</v>
+        <v>-1.20247026120297</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.9434266931129</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.411045903890353</v>
+        <v>1.402582051591381</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.19794448465086</v>
+        <v>-11.06855160259498</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.312371377613713</v>
+        <v>-1.26061422479136</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.9434266931129</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.409570676991611</v>
+        <v>1.401106824692639</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.14835364022603</v>
+        <v>-11.01896075817015</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.277481629678908</v>
+        <v>-1.225724476856554</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.87972942818978</v>
+        <v>-2.893835848688066</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.454378593811384</v>
+        <v>1.445914741512412</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.13554624722125</v>
+        <v>-11.00615336516537</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.285409806123681</v>
+        <v>-1.233652653301327</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.928585203198681</v>
+        <v>-2.942691623696966</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.41201399515936</v>
+        <v>1.403550142860389</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.90970109450184</v>
+        <v>-10.78030821244596</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.185492671999709</v>
+        <v>-1.133735519177355</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.900764948109803</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.446749073547867</v>
+        <v>1.438285221248895</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.78512243816425</v>
+        <v>-10.65572955610837</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.134522064908613</v>
+        <v>-1.082764912086259</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.900764948109803</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447888218103926</v>
+        <v>1.439424365804954</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.83801772620854</v>
+        <v>-10.70862484415265</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.153046405964219</v>
+        <v>-1.101289253141865</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.895809602021357</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.453495199919101</v>
+        <v>1.44503134762013</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.76588455092066</v>
+        <v>-10.63649166886477</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.118459431610431</v>
+        <v>-1.066702278788076</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.895809602021357</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.459228904157738</v>
+        <v>1.450765051858766</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.69451815831101</v>
+        <v>-10.56512527625513</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.099650136960437</v>
+        <v>-1.047892984138083</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.824443209411708</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.492311477329662</v>
+        <v>1.48384762503069</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.43068129110694</v>
+        <v>-10.30128840905106</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.003998871391717</v>
+        <v>-0.9522417185693626</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.824443209411708</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.482427996016754</v>
+        <v>1.473964143717782</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.16343949023854</v>
+        <v>-10.03404660818266</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.898936711543731</v>
+        <v>-0.8471795587213768</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.824443209411708</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48059343551738</v>
+        <v>1.472129583218409</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.06553245156205</v>
+        <v>-9.936139569506167</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8600742110465958</v>
+        <v>-0.8083170582242416</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.742351039052866</v>
+        <v>-2.756457459551152</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.521084570460253</v>
+        <v>1.512620718161282</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.04157891058609</v>
+        <v>-9.912186028530209</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8498242885107188</v>
+        <v>-0.7980671356883651</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.718397498076909</v>
+        <v>-2.732503918575194</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.536125201191321</v>
+        <v>1.52766134889235</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.777518972263298</v>
+        <v>-9.648126090207413</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7574606293433526</v>
+        <v>-0.7057034765209984</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.468443980252399</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.672836995724275</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.070439348758461</v>
+        <v>-8.941046466702575</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4774158136017186</v>
+        <v>-0.4256586607793644</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.468443980252399</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.670049962063974</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.03025505039227</v>
+        <v>-8.900862168336385</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.460998470367401</v>
+        <v>-0.4092413175450469</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.428259681886208</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.69450416497153</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.866855179452909</v>
+        <v>-8.737462297397023</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3962717007708996</v>
+        <v>-0.3445145479485454</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.250753390448559</v>
+        <v>-2.264859810946845</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.800374761054876</v>
+        <v>1.791910908755905</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291807</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.633373957223309</v>
+        <v>-8.503981075167424</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2949547830412071</v>
+        <v>-0.243197630218853</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.017272168218961</v>
+        <v>-2.031378588717247</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.948387923230488</v>
+        <v>1.939924070931516</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.053768106021697</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.483707566215795</v>
+        <v>-8.35431468415991</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3400713447783685</v>
+        <v>-0.1862232841288067</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.924368676976425</v>
+        <v>-1.938475097474711</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.899146899835843</v>
+        <v>1.992773955364079</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390424</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.049135592768724</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.351432092584908</v>
+        <v>-8.222039210529022</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2917936685789866</v>
+        <v>-0.1379456079294248</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.792093203345538</v>
+        <v>-1.806199623843824</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.973879670761401</v>
+        <v>2.067506726289638</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105949</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.051950653456361</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.160832417911754</v>
+        <v>-8.031439535855869</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2127387380220882</v>
+        <v>-0.0588906773725264</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.601493528672385</v>
+        <v>-1.615599949170671</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.09105453625293</v>
+        <v>2.184681591781166</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.064856994680019</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.911832619228173</v>
+        <v>-7.782439737172288</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.100232477324997</v>
+        <v>0.05361558332456484</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.601493528672385</v>
+        <v>-1.615599949170671</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.103960877476589</v>
+        <v>2.197587933004825</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.936881065080801</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.017422609001278</v>
+        <v>-7.888029726945392</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2704444028334576</v>
+        <v>-0.1165963421838958</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.70708351844549</v>
+        <v>-1.721189938943775</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.912630954013507</v>
+        <v>2.006258009541743</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.985425406957887</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.036157511119875</v>
+        <v>-7.906764629063989</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.22939402180381</v>
+        <v>-0.07554596115424816</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.712679528105621</v>
+        <v>-1.726785948603907</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.957817690094515</v>
+        <v>2.051444745622751</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710807</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.86554648426972</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.888217469712275</v>
+        <v>-7.75882458765639</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2900969279289378</v>
+        <v>-0.136248867279376</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.692358612197063</v>
+        <v>-1.706465032695349</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.850131316951482</v>
+        <v>1.943758372479718</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.856832498016241</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.871059319580981</v>
+        <v>-7.741666437525096</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2919476541298982</v>
+        <v>-0.1380995934803364</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.689306882564055</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.85171222077678</v>
+        <v>1.945339276305016</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.849871885921148</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.827510912810291</v>
+        <v>-7.698118030754405</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2814889035167152</v>
+        <v>-0.1276408428671534</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.689306882564055</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.844751608681687</v>
+        <v>1.938378664209923</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.864334240302291</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.585362519356432</v>
+        <v>-7.455969637300547</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1701671917540288</v>
+        <v>-0.01631913110446703</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.689306882564055</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.85921396306283</v>
+        <v>1.952841018591066</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722815</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.858866360761486</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.477103382233911</v>
+        <v>-7.347710500178025</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1323314164458251</v>
+        <v>0.02151664420373667</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.689306882564055</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.853746083522025</v>
+        <v>1.947373139050261</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.856364454772063</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.35381224741678</v>
+        <v>-7.224419365360895</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.08551686850839602</v>
+        <v>0.06833119214116579</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.551909327248639</v>
+        <v>-1.566015747746925</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.92521885842288</v>
+        <v>2.018845913951116</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.864065433009388</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.332663048513337</v>
+        <v>-7.203270166457451</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.06935621070969367</v>
+        <v>0.08449184993986814</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.530760128345195</v>
+        <v>-1.544866548843481</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.945609356002271</v>
+        <v>2.039236411530508</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.859846141356439</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.088897606529892</v>
+        <v>-6.959504724474007</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.02393067443073482</v>
+        <v>0.1777787350802966</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.530760128345195</v>
+        <v>-1.544866548843481</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.941390064349322</v>
+        <v>2.035017119877558</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.861970455276455</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.987134786252597</v>
+        <v>-6.857741904196712</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.06676011646166868</v>
+        <v>0.2206081771112305</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.517541059952767</v>
+        <v>-1.531647480451052</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.951445819304795</v>
+        <v>2.045072874833032</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279181</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.854712530260157</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.737284392303523</v>
+        <v>-6.607891510247637</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1594423490250008</v>
+        <v>0.3132904096745626</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.517541059952767</v>
+        <v>-1.531647480451052</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.944187894288498</v>
+        <v>2.037814949816734</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.858311653780806</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.56139229983609</v>
+        <v>-6.431999417780204</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2333983095326229</v>
+        <v>0.3872463701821847</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.517541059952767</v>
+        <v>-1.531647480451052</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.947787017809146</v>
+        <v>2.041414073337382</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.87163915983536</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.389945836813626</v>
+        <v>-6.260552954757741</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3153044007961618</v>
+        <v>0.4691524614457236</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.346094596930303</v>
+        <v>-1.360201017428589</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.063982401677178</v>
+        <v>2.157609457205414</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.870659637451657</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.164912837144803</v>
+        <v>-6.035519955088918</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4043380782799879</v>
+        <v>0.5581861389295497</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.12106159726148</v>
+        <v>-1.135168017759766</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.198022679094769</v>
+        <v>2.291649734623005</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.875354438505974</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.101277094910869</v>
+        <v>-5.971884212854984</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4344871762278788</v>
+        <v>0.588335236877441</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.057425855027546</v>
+        <v>-1.071532275525832</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.240898925489446</v>
+        <v>2.334525981017683</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.85654869728977</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.057514913605027</v>
+        <v>-5.928122031549142</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4331863075340112</v>
+        <v>0.587034368183573</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.057425855027546</v>
+        <v>-1.071532275525832</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.222093184273242</v>
+        <v>2.315720239801478</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.858291773914647</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.817084416800167</v>
+        <v>-5.687691534744282</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.531101582880833</v>
+        <v>0.6849496435303948</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8169953582226857</v>
+        <v>-0.8311017787209716</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.368094558981036</v>
+        <v>2.461721614509272</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.862221087749467</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.744841848628973</v>
+        <v>-5.615448966573087</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5639279239841311</v>
+        <v>0.7177759846336929</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8169953582226857</v>
+        <v>-0.8311017787209716</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.372023872815856</v>
+        <v>2.465650928344092</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.862899671666807</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.691843526347585</v>
+        <v>-5.562450644291699</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5858058368140262</v>
+        <v>0.739653897463588</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7616590992207468</v>
+        <v>-0.7757655197190327</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.405904212134359</v>
+        <v>2.499531267662595</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.859897742886801</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.583038640867858</v>
+        <v>-5.453645758811972</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6263258622259102</v>
+        <v>0.780173922875472</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7616590992207468</v>
+        <v>-0.7757655197190327</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.402902283354353</v>
+        <v>2.496529338882589</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.861476779897415</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.363017842830847</v>
+        <v>-5.233624960774962</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7159132184513286</v>
+        <v>0.8697612791008904</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6204392541527666</v>
+        <v>-0.6345456746510525</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.489213227405755</v>
+        <v>2.582840282933991</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.877370962699238</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.230150153767569</v>
+        <v>-5.100757271711684</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.7849544768784629</v>
+        <v>0.9388025375280247</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6204392541527666</v>
+        <v>-0.6345456746510525</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.505107410207578</v>
+        <v>2.598734465735815</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.87851680713954</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.109977070403071</v>
+        <v>-4.980584188347185</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8341695546645642</v>
+        <v>0.9880176153141262</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5002661707882676</v>
+        <v>-0.5143725912865535</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.57835710466658</v>
+        <v>2.671984160194816</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.88860490970098</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.965304925303333</v>
+        <v>-4.835912043247448</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9021265152658993</v>
+        <v>1.055974575915461</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3555940256885302</v>
+        <v>-0.3697004461868161</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.675248494287862</v>
+        <v>2.768875549816098</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.874642401102406</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.025179752661026</v>
+        <v>-4.89578687060514</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.8642140757242482</v>
+        <v>1.01806213637381</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4154688530462223</v>
+        <v>-0.4295752735445083</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.625361089274672</v>
+        <v>2.718988144802909</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.897042894424972</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.938380254882016</v>
+        <v>-4.808987372826131</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9213343681584178</v>
+        <v>1.07518242880798</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4154688530462223</v>
+        <v>-0.4295752735445083</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.647761582597238</v>
+        <v>2.741388638125475</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.897115295798384</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.940849961343822</v>
+        <v>-4.811457079287937</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9204188869471077</v>
+        <v>1.07426694759667</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4179385595080285</v>
+        <v>-0.4320449800063144</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.646352160093567</v>
+        <v>2.739979215621803</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.908122218273086</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.009220147667833</v>
+        <v>-4.879827265611947</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9040777348922058</v>
+        <v>1.057925795541767</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4086628604718135</v>
+        <v>-0.4227692809700995</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.662924501989998</v>
+        <v>2.756551557518234</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.898558926904977</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.117758328583967</v>
+        <v>-4.988365446528081</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8510991711576432</v>
+        <v>1.004947231807205</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4086628604718135</v>
+        <v>-0.4227692809700995</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.653361210621889</v>
+        <v>2.746988266150125</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.723268491945364</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.148751487912672</v>
+        <v>-5.019358605856787</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.6634114724665481</v>
+        <v>0.8172595331161099</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4086628604718135</v>
+        <v>-0.4227692809700995</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.478070775662276</v>
+        <v>2.571697831190512</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.727835723937152</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.973277228120203</v>
+        <v>-4.843884346064318</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7381684083753233</v>
+        <v>0.8920164690248851</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4086628604718135</v>
+        <v>-0.4227692809700995</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.482638007654064</v>
+        <v>2.5762650631823</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.703577752698359</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.084213480761452</v>
+        <v>-4.954820598705567</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.6695359360800306</v>
+        <v>0.8233839967295926</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4086628604718135</v>
+        <v>-0.4227692809700995</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.458380036415271</v>
+        <v>2.552007091943507</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.706709137918264</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.092495554906511</v>
+        <v>-4.963102672850625</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6693544916419127</v>
+        <v>0.8232025522914748</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4169449346168719</v>
+        <v>-0.4310513551151579</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.456542177148142</v>
+        <v>2.550169232676378</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.716881524350397</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.934569955971218</v>
+        <v>-4.805177073915332</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7426971176481625</v>
+        <v>0.8965451782977243</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4169449346168719</v>
+        <v>-0.4310513551151579</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.466714563580274</v>
+        <v>2.56034161910851</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742296</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.711827794924257</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.894729045099032</v>
+        <v>-4.718933610888954</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7535797525708969</v>
+        <v>0.9259888340821356</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4169449346168719</v>
+        <v>-0.4310513551151579</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.461660834154134</v>
+        <v>2.55528788968237</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.703603570368783</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.940035864498012</v>
+        <v>-4.764240430287934</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7272328002558306</v>
+        <v>0.8996418817670693</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4577550976261027</v>
+        <v>-0.4718615181243886</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.428950511793121</v>
+        <v>2.522577567321358</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803188</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.704155443401884</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.969068969200313</v>
+        <v>-4.793273534990235</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7161714314080116</v>
+        <v>0.8885805129192503</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4577550976261027</v>
+        <v>-0.4718615181243886</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.429502384826223</v>
+        <v>2.523129440354459</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.63342813529325</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.876258487749453</v>
+        <v>-4.700463053539376</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6825683158797213</v>
+        <v>0.85497739739096</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3649446161752434</v>
+        <v>-0.3790510366735293</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.414461365588104</v>
+        <v>2.50808842111634</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.635301611217851</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.920647957078881</v>
+        <v>-4.744852522868803</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6666860040725511</v>
+        <v>0.8390950855837898</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.409334085504671</v>
+        <v>-0.423440506002957</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.389701159915048</v>
+        <v>2.483328215443284</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472735</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.630377319729574</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.807976738842631</v>
+        <v>-4.632181304632553</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.706830199878774</v>
+        <v>0.8792392813900127</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2966628672684208</v>
+        <v>-0.3107692877667068</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.452379599368522</v>
+        <v>2.546006654896757</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.635868615560241</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.695599737659958</v>
+        <v>-4.51980430344988</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7572722961825105</v>
+        <v>0.9296813776937491</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2966628672684208</v>
+        <v>-0.3107692877667068</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.457870895199189</v>
+        <v>2.551497950727425</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.64736581732878</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.893834306546688</v>
+        <v>-4.718038872336611</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6894756703963574</v>
+        <v>0.8618847519075961</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4948974361551514</v>
+        <v>-0.5090038566534374</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.35042735563569</v>
+        <v>2.444054411163926</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.485721537329433</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.976835587571967</v>
+        <v>-4.80104015336189</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4946308779868991</v>
+        <v>0.6670399594981378</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5134683206823252</v>
+        <v>-0.5275747411806111</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.177640544920038</v>
+        <v>2.271267600448275</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.605871198048639</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.085449666015299</v>
+        <v>-4.909654231805221</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5713349073287723</v>
+        <v>0.7437439888400108</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5134683206823252</v>
+        <v>-0.5275747411806111</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.297790205639244</v>
+        <v>2.39141726116748</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.620384224150962</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.172048248996401</v>
+        <v>-4.996252814786324</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.551208500238654</v>
+        <v>0.7236175817498927</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5134683206823252</v>
+        <v>-0.5275747411806111</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.312303231741567</v>
+        <v>2.405930287269803</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.617803665493331</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.13366458643825</v>
+        <v>-4.957869152228173</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5639814066042832</v>
+        <v>0.7363904881155219</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.475084658124174</v>
+        <v>-0.4891910786224599</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.332752870618827</v>
+        <v>2.426379926147062</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.614532694338632</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.956548256403084</v>
+        <v>-4.780752822193007</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6315569674636514</v>
+        <v>0.8039660489748901</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.475084658124174</v>
+        <v>-0.4891910786224599</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.329481899464128</v>
+        <v>2.423108954992364</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.615216086100546</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.00164050123663</v>
+        <v>-4.825845067026552</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6142034612921463</v>
+        <v>0.786612542803385</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5369807012935638</v>
+        <v>-0.5510871217918497</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.293027665324407</v>
+        <v>2.386654720852644</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.60900306140696</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.822265079997862</v>
+        <v>-4.646469645787785</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6797406050940678</v>
+        <v>0.8521496866053064</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3802039431228451</v>
+        <v>-0.394310363621131</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.380880695533253</v>
+        <v>2.474507751061489</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.58981051673855</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.867279293518468</v>
+        <v>-4.691483859308391</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6425423750174151</v>
+        <v>0.8149514565286535</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4105528384374497</v>
+        <v>-0.4246592589357356</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.34347881367608</v>
+        <v>2.437105869204316</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.595502079077495</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.134283803790903</v>
+        <v>-4.958488369580826</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5414321332473868</v>
+        <v>0.7138412147586253</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6049158764803984</v>
+        <v>-0.6190222969786843</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.232552553189257</v>
+        <v>2.326179608717493</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760807</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.594706000973997</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.235481585228076</v>
+        <v>-5.059686151017999</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5001569425690193</v>
+        <v>0.6725660240802576</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6733246900257175</v>
+        <v>-0.6874311105240034</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.190711186958567</v>
+        <v>2.284338242486803</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.667265825912802</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.203005999057304</v>
+        <v>-5.106281231509914</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5857070019761332</v>
+        <v>0.651527953437808</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6733246900257175</v>
+        <v>-0.6874311105240034</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.263271011897372</v>
+        <v>2.281938204041119</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.663790545121047</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.183967871350006</v>
+        <v>-5.087243103802617</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5898469722672974</v>
+        <v>0.6556679237289722</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.731508301356912</v>
+        <v>-0.7456147218551979</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.2248855643069</v>
+        <v>2.243552756450648</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.841372414059728</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.215094502500625</v>
+        <v>-5.118369734953236</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7549781887457305</v>
+        <v>0.8207991402074053</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.731508301356912</v>
+        <v>-0.7456147218551979</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.402467433245581</v>
+        <v>2.421134625389328</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.842205743045861</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.267414883101416</v>
+        <v>-5.170690115554027</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7348833654915472</v>
+        <v>0.800704316953222</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6965614413480399</v>
+        <v>-0.7106678618463258</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.424268878237037</v>
+        <v>2.442936070380785</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.848214273442787</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.287672181630374</v>
+        <v>-5.190947414082985</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7327889764768902</v>
+        <v>0.798609927938565</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6965614413480399</v>
+        <v>-0.7106678618463258</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.430277408633963</v>
+        <v>2.448944600777711</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.927366921234809</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.139929211395372</v>
+        <v>-5.043204443847983</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8710388123629129</v>
+        <v>0.9368597638245877</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5287540841131567</v>
+        <v>-0.5428605046114426</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.610114470766915</v>
+        <v>2.628781662910663</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.93016054276629</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.241943893926593</v>
+        <v>-5.145219126379204</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8330265608819056</v>
+        <v>0.8988475123435804</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5287540841131567</v>
+        <v>-0.5428605046114426</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.612908092298396</v>
+        <v>2.631575284442144</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.930822891157948</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.235791187873809</v>
+        <v>-5.13906642032642</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8361499916946777</v>
+        <v>0.9019709431563525</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5226013780603724</v>
+        <v>-0.5367077985586584</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.617262064321725</v>
+        <v>2.635929256465473</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.929903367898059</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.252600486024311</v>
+        <v>-5.155875718476921</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8285067491745872</v>
+        <v>0.894327700636262</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.5394106762108741</v>
+        <v>-0.5535170967091601</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.606256962171535</v>
+        <v>2.624924154315282</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.996238921694879</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.190302487248188</v>
+        <v>-5.093577719700799</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9197615024818568</v>
+        <v>0.9855824539435316</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.5394106762108741</v>
+        <v>-0.5535170967091601</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.672592515968355</v>
+        <v>2.691259708112103</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.704819794084278</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.988512289583031</v>
+        <v>-4.891787522035641</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7090584539373181</v>
+        <v>0.7748794053989929</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3413924840417197</v>
+        <v>-0.3554989045400057</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.499984303659246</v>
+        <v>2.518651495802994</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.775110026406453</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.928621607940437</v>
+        <v>-4.831896840393048</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8033049589165306</v>
+        <v>0.8691259103782054</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2815018023991263</v>
+        <v>-0.2956082228974122</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.606208944966977</v>
+        <v>2.624876137110725</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.789737762522496</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.026362152565412</v>
+        <v>-4.929637385018022</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7788364771825846</v>
+        <v>0.8446574286442592</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2973910805321064</v>
+        <v>-0.3114975010303924</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.611303114203233</v>
+        <v>2.62997030634698</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.788273743347168</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.202699912688341</v>
+        <v>-5.105975145140952</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7068373539580843</v>
+        <v>0.7726583054197591</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4737288406550358</v>
+        <v>-0.4878352611533218</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.504036438954147</v>
+        <v>2.522703631097894</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.786765361387097</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.131153589911464</v>
+        <v>-5.034428822364075</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7339475011087639</v>
+        <v>0.7997684525704387</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4737288406550358</v>
+        <v>-0.4878352611533218</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.502528056994076</v>
+        <v>2.521195249137823</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102496</v>
+        <v>3.836023391024962</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.786628228822533</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.086780458272895</v>
+        <v>-4.990055690725506</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7515596211996276</v>
+        <v>0.8173805726613022</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4293557090164672</v>
+        <v>-0.4434621295147532</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.529014803412653</v>
+        <v>2.5476819955564</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.786628228822533</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.078826487978123</v>
+        <v>-4.982101720430734</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7547412093175363</v>
+        <v>0.8205621607792111</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4293557090164672</v>
+        <v>-0.4434621295147532</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.529014803412653</v>
+        <v>2.5476819955564</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.793009985850337</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.068453111645036</v>
+        <v>-4.971728344097647</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7652723168785753</v>
+        <v>0.8310932683402505</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.41898233268338</v>
+        <v>-0.4330887531816659</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.541620586240309</v>
+        <v>2.560287778384057</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.797902359225062</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.94076880185074</v>
+        <v>-4.844044034303351</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8212384141710185</v>
+        <v>0.8870593656326937</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2912980228890835</v>
+        <v>-0.3054044433873694</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.623123545491612</v>
+        <v>2.64179073763536</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.784657031700934</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.001435392253128</v>
+        <v>-4.904710624705739</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7837264504859354</v>
+        <v>0.8495474019476106</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3729963396076172</v>
+        <v>-0.3871027601059031</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.560859227936364</v>
+        <v>2.579526420080112</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.788754734311563</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.936441532319483</v>
+        <v>-4.839716764772094</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8138216970700221</v>
+        <v>0.8796426485316973</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3461657250034618</v>
+        <v>-0.3602721455017477</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.581055299309486</v>
+        <v>2.599722491453234</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.792915673942641</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.037200168076481</v>
+        <v>-4.940475400529092</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7776791823983009</v>
+        <v>0.8435001338599761</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4349912937304672</v>
+        <v>-0.4490977142287532</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.531920897704361</v>
+        <v>2.550588089848108</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.798795276470478</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.992997330990581</v>
+        <v>-4.896272563443191</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8012399197604982</v>
+        <v>0.8670608712221735</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.3907884566445668</v>
+        <v>-0.4048948771428527</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.564322202483738</v>
+        <v>2.582989394627486</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.797205276939725</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.029976358654023</v>
+        <v>-4.933251591106634</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7848583091643686</v>
+        <v>0.8506792606260438</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.3538145548532363</v>
+        <v>-0.3679209753515222</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.584916544027784</v>
+        <v>2.603583736171532</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.848453042122765</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.050034437518864</v>
+        <v>-4.953309669971475</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8280828428014719</v>
+        <v>0.8939037942631474</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.3538145548532363</v>
+        <v>-0.3679209753515222</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.636164309210824</v>
+        <v>2.654831501354571</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.846893746717018</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.010103764340974</v>
+        <v>-4.913378996793584</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8424958166668812</v>
+        <v>0.9083167681285567</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.3138838816753459</v>
+        <v>-0.3279903021736318</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.658563417711811</v>
+        <v>2.677230609855559</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864518876232396</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.841841974955288</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.969633416778269</v>
+        <v>-4.87290864923088</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.8536321839302334</v>
+        <v>0.9194531353919086</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.273413534112641</v>
+        <v>-0.2875199546109269</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.677793854487704</v>
+        <v>2.696461046631452</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842576394162111</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.859029379047993</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.904409235651063</v>
+        <v>-4.807684468103674</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8969092604738205</v>
+        <v>0.9627302119354957</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.2081893529854353</v>
+        <v>-0.2222957734837213</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.734115767256732</v>
+        <v>2.75278295940048</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840090220639817</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.854990351347273</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.95490352600812</v>
+        <v>-4.85817875846073</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8726725166302782</v>
+        <v>0.9384934680919534</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.2532100901115096</v>
+        <v>-0.2673165106097955</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.703064297280368</v>
+        <v>2.721731489424116</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.856247143678514</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.975015182042828</v>
+        <v>-4.878290414495439</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8658846465476353</v>
+        <v>0.9317055980093105</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.2421827451140904</v>
+        <v>-0.2562891656123763</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.71093749661006</v>
+        <v>2.729604688753808</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.016804914699724</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.072695761315474</v>
+        <v>-4.975970993768085</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.9873701858597874</v>
+        <v>1.053191137321463</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.3528859404542792</v>
+        <v>-0.3669923609525651</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.805073350427157</v>
+        <v>2.823740542570905</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.136917823917542</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.048904192709331</v>
+        <v>-4.952179425161942</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.116999722520062</v>
+        <v>1.182820673981737</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.3290943718481369</v>
+        <v>-0.3432007923464228</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.93946120080866</v>
+        <v>2.958128392952408</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.71523504607733</v>
+        <v>3.814259761756012</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.128625799931401</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-5.085658611271054</v>
+        <v>-4.988933843723665</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.094005931109232</v>
+        <v>1.159826882570907</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.3290943718481369</v>
+        <v>-0.3432007923464228</v>
       </c>
       <c r="G1993" t="n">
-        <v>2.931169176822519</v>
+        <v>2.949836368966267</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.720049849500817</v>
+        <v>3.785009351048036</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.25677692125008</v>
+        <v>3.05922572275841</v>
       </c>
       <c r="D1994" t="n">
-        <v>-5.070772598716863</v>
+        <v>-5.147399890315448</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.228111457449587</v>
+        <v>0.9999093423184835</v>
       </c>
       <c r="F1994" t="n">
-        <v>-0.3290943718481369</v>
+        <v>-0.501666838938206</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.059320298141198</v>
+        <v>2.758225619395487</v>
       </c>
     </row>
   </sheetData>
